--- a/V9_W8_B32/data_instructions/VLIW_Excel/Unit13_1_DownSamplingL.xlsx
+++ b/V9_W8_B32/data_instructions/VLIW_Excel/Unit13_1_DownSamplingL.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legoa\NCU\專題\專題內容\組譯器\WeightBiasRearranger\V7\data_instructions\VLIW_Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legoa\NCU\專題\專題內容\組譯器\WeightBiasRearranger\V9_W8_B32\data_instructions\VLIW_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9A84E9-F266-44C3-AD31-6C7DA54E5FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1190F9E8-20F8-491C-95F2-9DA22360F115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{8075A957-5B64-468D-B2D4-F19799456396}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{8075A957-5B64-468D-B2D4-F19799456396}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="87">
   <si>
     <t>OP_Code</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -382,6 +382,10 @@
   </si>
   <si>
     <t>8*(192/4)*3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Requant_Sel[3]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -613,7 +617,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -625,10 +632,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1094,6 +1098,9 @@
       <c r="M5" s="8" t="s">
         <v>81</v>
       </c>
+      <c r="N5" s="7" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B7" s="6" t="s">
@@ -1104,7 +1111,7 @@
       </c>
       <c r="D7" s="22"/>
       <c r="E7" s="22"/>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="23" t="s">
         <v>26</v>
       </c>
       <c r="G7" s="22"/>
@@ -1139,7 +1146,7 @@
       <c r="C8" s="22"/>
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
-      <c r="F8" s="28"/>
+      <c r="F8" s="23"/>
       <c r="G8" s="22"/>
       <c r="H8" s="22"/>
       <c r="I8" s="22"/>
@@ -1185,7 +1192,7 @@
       <c r="C9" s="22"/>
       <c r="D9" s="22"/>
       <c r="E9" s="22"/>
-      <c r="F9" s="28"/>
+      <c r="F9" s="23"/>
       <c r="G9" s="22"/>
       <c r="H9" s="22"/>
       <c r="I9" s="22"/>
@@ -1209,7 +1216,7 @@
       <c r="C10" s="22"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22"/>
-      <c r="F10" s="28"/>
+      <c r="F10" s="23"/>
       <c r="G10" s="22"/>
       <c r="H10" s="22"/>
       <c r="I10" s="22"/>
@@ -1240,7 +1247,7 @@
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
       <c r="E11" s="22"/>
-      <c r="F11" s="28"/>
+      <c r="F11" s="23"/>
       <c r="G11" s="22"/>
       <c r="H11" s="22"/>
       <c r="I11" s="22"/>
@@ -1274,7 +1281,7 @@
       <c r="F12" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="G12" s="28" t="s">
+      <c r="G12" s="23" t="s">
         <v>26</v>
       </c>
       <c r="H12" s="22"/>
@@ -1309,7 +1316,7 @@
       <c r="D13" s="22"/>
       <c r="E13" s="22"/>
       <c r="F13" s="22"/>
-      <c r="G13" s="28"/>
+      <c r="G13" s="23"/>
       <c r="H13" s="22"/>
       <c r="I13" s="22"/>
       <c r="J13" s="22"/>
@@ -1352,7 +1359,7 @@
       <c r="D14" s="22"/>
       <c r="E14" s="22"/>
       <c r="F14" s="22"/>
-      <c r="G14" s="28"/>
+      <c r="G14" s="23"/>
       <c r="H14" s="22"/>
       <c r="I14" s="22"/>
       <c r="J14" s="22"/>
@@ -1376,7 +1383,7 @@
       <c r="D15" s="22"/>
       <c r="E15" s="22"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="28"/>
+      <c r="G15" s="23"/>
       <c r="H15" s="22"/>
       <c r="I15" s="22"/>
       <c r="J15" s="22"/>
@@ -1407,7 +1414,7 @@
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
-      <c r="G16" s="28"/>
+      <c r="G16" s="23"/>
       <c r="H16" s="22"/>
       <c r="I16" s="22"/>
       <c r="J16" s="22"/>
@@ -1434,14 +1441,14 @@
       </c>
       <c r="D17" s="22"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="26" t="s">
+      <c r="F17" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="26" t="s">
+      <c r="G17" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H17" s="22"/>
-      <c r="I17" s="27" t="s">
+      <c r="I17" s="24" t="s">
         <v>26</v>
       </c>
       <c r="J17" s="22"/>
@@ -1470,10 +1477,10 @@
       <c r="C18" s="22"/>
       <c r="D18" s="22"/>
       <c r="E18" s="22"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
       <c r="H18" s="22"/>
-      <c r="I18" s="27"/>
+      <c r="I18" s="24"/>
       <c r="J18" s="22"/>
       <c r="L18" s="11" t="s">
         <v>5</v>
@@ -1513,10 +1520,10 @@
       <c r="C19" s="22"/>
       <c r="D19" s="22"/>
       <c r="E19" s="22"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
       <c r="H19" s="22"/>
-      <c r="I19" s="27"/>
+      <c r="I19" s="24"/>
       <c r="J19" s="22"/>
       <c r="L19" s="12" t="s">
         <v>15</v>
@@ -1546,10 +1553,10 @@
       <c r="C20" s="22"/>
       <c r="D20" s="22"/>
       <c r="E20" s="22"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
       <c r="H20" s="22"/>
-      <c r="I20" s="27"/>
+      <c r="I20" s="24"/>
       <c r="J20" s="22"/>
       <c r="L20" s="14" t="s">
         <v>17</v>
@@ -1576,10 +1583,10 @@
       <c r="C21" s="22"/>
       <c r="D21" s="22"/>
       <c r="E21" s="22"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
       <c r="H21" s="22"/>
-      <c r="I21" s="27"/>
+      <c r="I21" s="24"/>
       <c r="J21" s="22"/>
       <c r="L21" s="15" t="s">
         <v>23</v>
@@ -1626,10 +1633,10 @@
       <c r="G24" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="H24" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="I24" s="24" t="s">
+      <c r="H24" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" s="25" t="s">
         <v>40</v>
       </c>
       <c r="J24" s="22"/>
@@ -1663,8 +1670,8 @@
       <c r="E25" s="22"/>
       <c r="F25" s="22"/>
       <c r="G25" s="22"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="25"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="26"/>
       <c r="J25" s="22"/>
       <c r="L25" s="11" t="s">
         <v>5</v>
@@ -1706,8 +1713,8 @@
       <c r="E26" s="22"/>
       <c r="F26" s="22"/>
       <c r="G26" s="22"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="25"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="26"/>
       <c r="J26" s="22"/>
       <c r="L26" s="12" t="s">
         <v>15</v>
@@ -1730,8 +1737,8 @@
       <c r="E27" s="22"/>
       <c r="F27" s="22"/>
       <c r="G27" s="22"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="25"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="26"/>
       <c r="J27" s="22"/>
       <c r="L27" s="14" t="s">
         <v>17</v>
@@ -1761,8 +1768,8 @@
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
       <c r="G28" s="22"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="25"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="26"/>
       <c r="J28" s="22"/>
       <c r="L28" s="15" t="s">
         <v>23</v>
@@ -1790,7 +1797,7 @@
       </c>
       <c r="D29" s="22"/>
       <c r="E29" s="22"/>
-      <c r="F29" s="28" t="s">
+      <c r="F29" s="23" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="22" t="s">
@@ -1799,10 +1806,10 @@
       <c r="H29" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="I29" s="26" t="s">
+      <c r="I29" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="J29" s="27" t="s">
+      <c r="J29" s="24" t="s">
         <v>26</v>
       </c>
       <c r="L29" s="9" t="s">
@@ -1833,11 +1840,11 @@
       <c r="C30" s="22"/>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
-      <c r="F30" s="28"/>
+      <c r="F30" s="23"/>
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="24"/>
       <c r="L30" s="11" t="s">
         <v>5</v>
       </c>
@@ -1876,11 +1883,11 @@
       <c r="C31" s="22"/>
       <c r="D31" s="22"/>
       <c r="E31" s="22"/>
-      <c r="F31" s="28"/>
+      <c r="F31" s="23"/>
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="27"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="24"/>
       <c r="L31" s="12" t="s">
         <v>15</v>
       </c>
@@ -1909,11 +1916,11 @@
       <c r="C32" s="22"/>
       <c r="D32" s="22"/>
       <c r="E32" s="22"/>
-      <c r="F32" s="28"/>
+      <c r="F32" s="23"/>
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="24"/>
       <c r="L32" s="14" t="s">
         <v>17</v>
       </c>
@@ -1940,11 +1947,11 @@
       <c r="C33" s="22"/>
       <c r="D33" s="22"/>
       <c r="E33" s="22"/>
-      <c r="F33" s="28"/>
+      <c r="F33" s="23"/>
       <c r="G33" s="22"/>
       <c r="H33" s="22"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="27"/>
+      <c r="I33" s="27"/>
+      <c r="J33" s="24"/>
       <c r="L33" s="15" t="s">
         <v>23</v>
       </c>
@@ -1971,19 +1978,19 @@
       </c>
       <c r="D34" s="22"/>
       <c r="E34" s="22"/>
-      <c r="F34" s="26" t="s">
+      <c r="F34" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="G34" s="26" t="s">
+      <c r="G34" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="H34" s="26" t="s">
+      <c r="H34" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I34" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="J34" s="23" t="s">
+      <c r="I34" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="J34" s="28" t="s">
         <v>34</v>
       </c>
       <c r="L34" s="9" t="s">
@@ -2014,11 +2021,11 @@
       <c r="C35" s="22"/>
       <c r="D35" s="22"/>
       <c r="E35" s="22"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="27"/>
-      <c r="J35" s="23"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="28"/>
       <c r="L35" s="11" t="s">
         <v>5</v>
       </c>
@@ -2060,11 +2067,11 @@
       <c r="C36" s="22"/>
       <c r="D36" s="22"/>
       <c r="E36" s="22"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="27"/>
-      <c r="J36" s="23"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="28"/>
       <c r="L36" s="12" t="s">
         <v>15</v>
       </c>
@@ -2093,11 +2100,11 @@
       <c r="C37" s="22"/>
       <c r="D37" s="22"/>
       <c r="E37" s="22"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="23"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="28"/>
       <c r="L37" s="14" t="s">
         <v>17</v>
       </c>
@@ -2124,11 +2131,11 @@
       <c r="C38" s="22"/>
       <c r="D38" s="22"/>
       <c r="E38" s="22"/>
-      <c r="F38" s="26"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="27"/>
-      <c r="J38" s="23"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="28"/>
       <c r="L38" s="15" t="s">
         <v>23</v>
       </c>
@@ -2161,11 +2168,11 @@
       <c r="F40" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="G40" s="28" t="s">
+      <c r="G40" s="23" t="s">
         <v>26</v>
       </c>
       <c r="H40" s="22"/>
-      <c r="I40" s="24" t="s">
+      <c r="I40" s="25" t="s">
         <v>40</v>
       </c>
       <c r="J40" s="22"/>
@@ -2198,9 +2205,9 @@
       <c r="D41" s="22"/>
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
-      <c r="G41" s="28"/>
+      <c r="G41" s="23"/>
       <c r="H41" s="22"/>
-      <c r="I41" s="25"/>
+      <c r="I41" s="26"/>
       <c r="J41" s="22"/>
       <c r="L41" s="11" t="s">
         <v>5</v>
@@ -2241,9 +2248,9 @@
       <c r="D42" s="22"/>
       <c r="E42" s="22"/>
       <c r="F42" s="22"/>
-      <c r="G42" s="28"/>
+      <c r="G42" s="23"/>
       <c r="H42" s="22"/>
-      <c r="I42" s="25"/>
+      <c r="I42" s="26"/>
       <c r="J42" s="22"/>
       <c r="L42" s="12" t="s">
         <v>15</v>
@@ -2266,9 +2273,9 @@
       <c r="D43" s="22"/>
       <c r="E43" s="22"/>
       <c r="F43" s="22"/>
-      <c r="G43" s="28"/>
+      <c r="G43" s="23"/>
       <c r="H43" s="22"/>
-      <c r="I43" s="25"/>
+      <c r="I43" s="26"/>
       <c r="J43" s="22"/>
       <c r="L43" s="14" t="s">
         <v>17</v>
@@ -2297,9 +2304,9 @@
       <c r="D44" s="22"/>
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
-      <c r="G44" s="28"/>
+      <c r="G44" s="23"/>
       <c r="H44" s="22"/>
-      <c r="I44" s="25"/>
+      <c r="I44" s="26"/>
       <c r="J44" s="22"/>
       <c r="L44" s="15" t="s">
         <v>23</v>
@@ -2333,13 +2340,13 @@
       <c r="G45" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="H45" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="I45" s="26" t="s">
+      <c r="H45" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="I45" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="J45" s="27" t="s">
+      <c r="J45" s="24" t="s">
         <v>26</v>
       </c>
       <c r="L45" s="9" t="s">
@@ -2372,9 +2379,9 @@
       <c r="E46" s="22"/>
       <c r="F46" s="22"/>
       <c r="G46" s="22"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="26"/>
-      <c r="J46" s="27"/>
+      <c r="H46" s="23"/>
+      <c r="I46" s="27"/>
+      <c r="J46" s="24"/>
       <c r="L46" s="11" t="s">
         <v>5</v>
       </c>
@@ -2415,9 +2422,9 @@
       <c r="E47" s="22"/>
       <c r="F47" s="22"/>
       <c r="G47" s="22"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="26"/>
-      <c r="J47" s="27"/>
+      <c r="H47" s="23"/>
+      <c r="I47" s="27"/>
+      <c r="J47" s="24"/>
       <c r="L47" s="12" t="s">
         <v>15</v>
       </c>
@@ -2448,9 +2455,9 @@
       <c r="E48" s="22"/>
       <c r="F48" s="22"/>
       <c r="G48" s="22"/>
-      <c r="H48" s="28"/>
-      <c r="I48" s="26"/>
-      <c r="J48" s="27"/>
+      <c r="H48" s="23"/>
+      <c r="I48" s="27"/>
+      <c r="J48" s="24"/>
       <c r="L48" s="14" t="s">
         <v>17</v>
       </c>
@@ -2479,9 +2486,9 @@
       <c r="E49" s="22"/>
       <c r="F49" s="22"/>
       <c r="G49" s="22"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="26"/>
-      <c r="J49" s="27"/>
+      <c r="H49" s="23"/>
+      <c r="I49" s="27"/>
+      <c r="J49" s="24"/>
       <c r="L49" s="15" t="s">
         <v>23</v>
       </c>
@@ -2508,19 +2515,19 @@
       </c>
       <c r="D50" s="22"/>
       <c r="E50" s="22"/>
-      <c r="F50" s="26" t="s">
+      <c r="F50" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="G50" s="26" t="s">
+      <c r="G50" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="H50" s="26" t="s">
+      <c r="H50" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I50" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="J50" s="23" t="s">
+      <c r="I50" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="J50" s="28" t="s">
         <v>34</v>
       </c>
       <c r="L50" s="9" t="s">
@@ -2551,11 +2558,11 @@
       <c r="C51" s="22"/>
       <c r="D51" s="22"/>
       <c r="E51" s="22"/>
-      <c r="F51" s="26"/>
-      <c r="G51" s="26"/>
-      <c r="H51" s="26"/>
-      <c r="I51" s="27"/>
-      <c r="J51" s="23"/>
+      <c r="F51" s="27"/>
+      <c r="G51" s="27"/>
+      <c r="H51" s="27"/>
+      <c r="I51" s="24"/>
+      <c r="J51" s="28"/>
       <c r="L51" s="11" t="s">
         <v>5</v>
       </c>
@@ -2594,11 +2601,11 @@
       <c r="C52" s="22"/>
       <c r="D52" s="22"/>
       <c r="E52" s="22"/>
-      <c r="F52" s="26"/>
-      <c r="G52" s="26"/>
-      <c r="H52" s="26"/>
-      <c r="I52" s="27"/>
-      <c r="J52" s="23"/>
+      <c r="F52" s="27"/>
+      <c r="G52" s="27"/>
+      <c r="H52" s="27"/>
+      <c r="I52" s="24"/>
+      <c r="J52" s="28"/>
       <c r="L52" s="12" t="s">
         <v>15</v>
       </c>
@@ -2627,11 +2634,11 @@
       <c r="C53" s="22"/>
       <c r="D53" s="22"/>
       <c r="E53" s="22"/>
-      <c r="F53" s="26"/>
-      <c r="G53" s="26"/>
-      <c r="H53" s="26"/>
-      <c r="I53" s="27"/>
-      <c r="J53" s="23"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="27"/>
+      <c r="H53" s="27"/>
+      <c r="I53" s="24"/>
+      <c r="J53" s="28"/>
       <c r="L53" s="14" t="s">
         <v>17</v>
       </c>
@@ -2658,11 +2665,11 @@
       <c r="C54" s="22"/>
       <c r="D54" s="22"/>
       <c r="E54" s="22"/>
-      <c r="F54" s="26"/>
-      <c r="G54" s="26"/>
-      <c r="H54" s="26"/>
-      <c r="I54" s="27"/>
-      <c r="J54" s="23"/>
+      <c r="F54" s="27"/>
+      <c r="G54" s="27"/>
+      <c r="H54" s="27"/>
+      <c r="I54" s="24"/>
+      <c r="J54" s="28"/>
       <c r="L54" s="15" t="s">
         <v>23</v>
       </c>
@@ -2692,14 +2699,14 @@
       </c>
       <c r="D56" s="22"/>
       <c r="E56" s="22"/>
-      <c r="F56" s="28" t="s">
+      <c r="F56" s="23" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="22"/>
       <c r="H56" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="I56" s="24" t="s">
+      <c r="I56" s="25" t="s">
         <v>40</v>
       </c>
       <c r="J56" s="22"/>
@@ -2731,10 +2738,10 @@
       <c r="C57" s="22"/>
       <c r="D57" s="22"/>
       <c r="E57" s="22"/>
-      <c r="F57" s="28"/>
+      <c r="F57" s="23"/>
       <c r="G57" s="22"/>
       <c r="H57" s="22"/>
-      <c r="I57" s="25"/>
+      <c r="I57" s="26"/>
       <c r="J57" s="22"/>
       <c r="L57" s="11" t="s">
         <v>5</v>
@@ -2774,10 +2781,10 @@
       <c r="C58" s="22"/>
       <c r="D58" s="22"/>
       <c r="E58" s="22"/>
-      <c r="F58" s="28"/>
+      <c r="F58" s="23"/>
       <c r="G58" s="22"/>
       <c r="H58" s="22"/>
-      <c r="I58" s="25"/>
+      <c r="I58" s="26"/>
       <c r="J58" s="22"/>
       <c r="L58" s="12" t="s">
         <v>15</v>
@@ -2799,10 +2806,10 @@
       <c r="C59" s="22"/>
       <c r="D59" s="22"/>
       <c r="E59" s="22"/>
-      <c r="F59" s="28"/>
+      <c r="F59" s="23"/>
       <c r="G59" s="22"/>
       <c r="H59" s="22"/>
-      <c r="I59" s="25"/>
+      <c r="I59" s="26"/>
       <c r="J59" s="22"/>
       <c r="L59" s="14" t="s">
         <v>17</v>
@@ -2830,10 +2837,10 @@
       <c r="C60" s="22"/>
       <c r="D60" s="22"/>
       <c r="E60" s="22"/>
-      <c r="F60" s="28"/>
+      <c r="F60" s="23"/>
       <c r="G60" s="22"/>
       <c r="H60" s="22"/>
-      <c r="I60" s="25"/>
+      <c r="I60" s="26"/>
       <c r="J60" s="22"/>
       <c r="L60" s="15" t="s">
         <v>23</v>
@@ -2864,16 +2871,16 @@
       <c r="F61" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="G61" s="28" t="s">
+      <c r="G61" s="23" t="s">
         <v>26</v>
       </c>
       <c r="H61" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="I61" s="26" t="s">
+      <c r="I61" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="J61" s="27" t="s">
+      <c r="J61" s="24" t="s">
         <v>26</v>
       </c>
       <c r="L61" s="9" t="s">
@@ -2905,10 +2912,10 @@
       <c r="D62" s="22"/>
       <c r="E62" s="22"/>
       <c r="F62" s="22"/>
-      <c r="G62" s="28"/>
+      <c r="G62" s="23"/>
       <c r="H62" s="22"/>
-      <c r="I62" s="26"/>
-      <c r="J62" s="27"/>
+      <c r="I62" s="27"/>
+      <c r="J62" s="24"/>
       <c r="L62" s="11" t="s">
         <v>5</v>
       </c>
@@ -2951,10 +2958,10 @@
       <c r="D63" s="22"/>
       <c r="E63" s="22"/>
       <c r="F63" s="22"/>
-      <c r="G63" s="28"/>
+      <c r="G63" s="23"/>
       <c r="H63" s="22"/>
-      <c r="I63" s="26"/>
-      <c r="J63" s="27"/>
+      <c r="I63" s="27"/>
+      <c r="J63" s="24"/>
       <c r="L63" s="12" t="s">
         <v>15</v>
       </c>
@@ -2984,10 +2991,10 @@
       <c r="D64" s="22"/>
       <c r="E64" s="22"/>
       <c r="F64" s="22"/>
-      <c r="G64" s="28"/>
+      <c r="G64" s="23"/>
       <c r="H64" s="22"/>
-      <c r="I64" s="26"/>
-      <c r="J64" s="27"/>
+      <c r="I64" s="27"/>
+      <c r="J64" s="24"/>
       <c r="L64" s="14" t="s">
         <v>17</v>
       </c>
@@ -3015,10 +3022,10 @@
       <c r="D65" s="22"/>
       <c r="E65" s="22"/>
       <c r="F65" s="22"/>
-      <c r="G65" s="28"/>
+      <c r="G65" s="23"/>
       <c r="H65" s="22"/>
-      <c r="I65" s="26"/>
-      <c r="J65" s="27"/>
+      <c r="I65" s="27"/>
+      <c r="J65" s="24"/>
       <c r="L65" s="15" t="s">
         <v>23</v>
       </c>
@@ -3045,19 +3052,19 @@
       </c>
       <c r="D66" s="22"/>
       <c r="E66" s="22"/>
-      <c r="F66" s="26" t="s">
+      <c r="F66" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="G66" s="26" t="s">
+      <c r="G66" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="H66" s="26" t="s">
+      <c r="H66" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I66" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="J66" s="23" t="s">
+      <c r="I66" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="J66" s="28" t="s">
         <v>34</v>
       </c>
       <c r="L66" s="9" t="s">
@@ -3088,11 +3095,11 @@
       <c r="C67" s="22"/>
       <c r="D67" s="22"/>
       <c r="E67" s="22"/>
-      <c r="F67" s="26"/>
-      <c r="G67" s="26"/>
-      <c r="H67" s="26"/>
-      <c r="I67" s="27"/>
-      <c r="J67" s="23"/>
+      <c r="F67" s="27"/>
+      <c r="G67" s="27"/>
+      <c r="H67" s="27"/>
+      <c r="I67" s="24"/>
+      <c r="J67" s="28"/>
       <c r="L67" s="11" t="s">
         <v>5</v>
       </c>
@@ -3131,11 +3138,11 @@
       <c r="C68" s="22"/>
       <c r="D68" s="22"/>
       <c r="E68" s="22"/>
-      <c r="F68" s="26"/>
-      <c r="G68" s="26"/>
-      <c r="H68" s="26"/>
-      <c r="I68" s="27"/>
-      <c r="J68" s="23"/>
+      <c r="F68" s="27"/>
+      <c r="G68" s="27"/>
+      <c r="H68" s="27"/>
+      <c r="I68" s="24"/>
+      <c r="J68" s="28"/>
       <c r="L68" s="12" t="s">
         <v>15</v>
       </c>
@@ -3164,11 +3171,11 @@
       <c r="C69" s="22"/>
       <c r="D69" s="22"/>
       <c r="E69" s="22"/>
-      <c r="F69" s="26"/>
-      <c r="G69" s="26"/>
-      <c r="H69" s="26"/>
-      <c r="I69" s="27"/>
-      <c r="J69" s="23"/>
+      <c r="F69" s="27"/>
+      <c r="G69" s="27"/>
+      <c r="H69" s="27"/>
+      <c r="I69" s="24"/>
+      <c r="J69" s="28"/>
       <c r="L69" s="14" t="s">
         <v>17</v>
       </c>
@@ -3195,11 +3202,11 @@
       <c r="C70" s="22"/>
       <c r="D70" s="22"/>
       <c r="E70" s="22"/>
-      <c r="F70" s="26"/>
-      <c r="G70" s="26"/>
-      <c r="H70" s="26"/>
-      <c r="I70" s="27"/>
-      <c r="J70" s="23"/>
+      <c r="F70" s="27"/>
+      <c r="G70" s="27"/>
+      <c r="H70" s="27"/>
+      <c r="I70" s="24"/>
+      <c r="J70" s="28"/>
       <c r="L70" s="15" t="s">
         <v>23</v>
       </c>
@@ -3250,7 +3257,7 @@
       <c r="F74" s="22"/>
       <c r="G74" s="22"/>
       <c r="H74" s="22"/>
-      <c r="I74" s="24" t="s">
+      <c r="I74" s="25" t="s">
         <v>40</v>
       </c>
       <c r="J74" s="22"/>
@@ -3282,7 +3289,7 @@
       <c r="F75" s="22"/>
       <c r="G75" s="22"/>
       <c r="H75" s="22"/>
-      <c r="I75" s="25"/>
+      <c r="I75" s="26"/>
       <c r="J75" s="22"/>
       <c r="L75" s="11" t="s">
         <v>5</v>
@@ -3325,7 +3332,7 @@
       <c r="F76" s="22"/>
       <c r="G76" s="22"/>
       <c r="H76" s="22"/>
-      <c r="I76" s="25"/>
+      <c r="I76" s="26"/>
       <c r="J76" s="22"/>
       <c r="L76" s="12" t="s">
         <v>15</v>
@@ -3350,7 +3357,7 @@
       <c r="F77" s="22"/>
       <c r="G77" s="22"/>
       <c r="H77" s="22"/>
-      <c r="I77" s="25"/>
+      <c r="I77" s="26"/>
       <c r="J77" s="22"/>
       <c r="L77" s="14" t="s">
         <v>17</v>
@@ -3380,7 +3387,7 @@
       <c r="F78" s="22"/>
       <c r="G78" s="22"/>
       <c r="H78" s="22"/>
-      <c r="I78" s="25"/>
+      <c r="I78" s="26"/>
       <c r="J78" s="22"/>
       <c r="L78" s="15" t="s">
         <v>23</v>
@@ -3406,10 +3413,10 @@
       <c r="F79" s="22"/>
       <c r="G79" s="22"/>
       <c r="H79" s="22"/>
-      <c r="I79" s="26" t="s">
+      <c r="I79" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="J79" s="27" t="s">
+      <c r="J79" s="24" t="s">
         <v>26</v>
       </c>
       <c r="L79" s="9" t="s">
@@ -3440,8 +3447,8 @@
       <c r="F80" s="22"/>
       <c r="G80" s="22"/>
       <c r="H80" s="22"/>
-      <c r="I80" s="26"/>
-      <c r="J80" s="27"/>
+      <c r="I80" s="27"/>
+      <c r="J80" s="24"/>
       <c r="L80" s="11" t="s">
         <v>5</v>
       </c>
@@ -3483,8 +3490,8 @@
       <c r="F81" s="22"/>
       <c r="G81" s="22"/>
       <c r="H81" s="22"/>
-      <c r="I81" s="26"/>
-      <c r="J81" s="27"/>
+      <c r="I81" s="27"/>
+      <c r="J81" s="24"/>
       <c r="L81" s="12" t="s">
         <v>15</v>
       </c>
@@ -3516,8 +3523,8 @@
       <c r="F82" s="22"/>
       <c r="G82" s="22"/>
       <c r="H82" s="22"/>
-      <c r="I82" s="26"/>
-      <c r="J82" s="27"/>
+      <c r="I82" s="27"/>
+      <c r="J82" s="24"/>
       <c r="L82" s="14" t="s">
         <v>17</v>
       </c>
@@ -3546,8 +3553,8 @@
       <c r="F83" s="22"/>
       <c r="G83" s="22"/>
       <c r="H83" s="22"/>
-      <c r="I83" s="26"/>
-      <c r="J83" s="27"/>
+      <c r="I83" s="27"/>
+      <c r="J83" s="24"/>
       <c r="L83" s="15" t="s">
         <v>23</v>
       </c>
@@ -3576,7 +3583,7 @@
       <c r="G84" s="22"/>
       <c r="H84" s="22"/>
       <c r="I84" s="22"/>
-      <c r="J84" s="23" t="s">
+      <c r="J84" s="28" t="s">
         <v>34</v>
       </c>
       <c r="L84" s="9" t="s">
@@ -3611,7 +3618,7 @@
       <c r="G85" s="22"/>
       <c r="H85" s="22"/>
       <c r="I85" s="22"/>
-      <c r="J85" s="23"/>
+      <c r="J85" s="28"/>
       <c r="L85" s="11" t="s">
         <v>5</v>
       </c>
@@ -3657,7 +3664,7 @@
       <c r="G86" s="22"/>
       <c r="H86" s="22"/>
       <c r="I86" s="22"/>
-      <c r="J86" s="23"/>
+      <c r="J86" s="28"/>
       <c r="L86" s="12" t="s">
         <v>15</v>
       </c>
@@ -3682,7 +3689,7 @@
       <c r="G87" s="22"/>
       <c r="H87" s="22"/>
       <c r="I87" s="22"/>
-      <c r="J87" s="23"/>
+      <c r="J87" s="28"/>
       <c r="L87" s="14" t="s">
         <v>17</v>
       </c>
@@ -3713,7 +3720,7 @@
       <c r="G88" s="22"/>
       <c r="H88" s="22"/>
       <c r="I88" s="22"/>
-      <c r="J88" s="23"/>
+      <c r="J88" s="28"/>
       <c r="L88" s="15" t="s">
         <v>23</v>
       </c>
@@ -3733,102 +3740,6 @@
     </row>
   </sheetData>
   <mergeCells count="120">
-    <mergeCell ref="I7:I11"/>
-    <mergeCell ref="J7:J11"/>
-    <mergeCell ref="C12:C16"/>
-    <mergeCell ref="D12:D16"/>
-    <mergeCell ref="E12:E16"/>
-    <mergeCell ref="F12:F16"/>
-    <mergeCell ref="G12:G16"/>
-    <mergeCell ref="H12:H16"/>
-    <mergeCell ref="I12:I16"/>
-    <mergeCell ref="J12:J16"/>
-    <mergeCell ref="C7:C11"/>
-    <mergeCell ref="D7:D11"/>
-    <mergeCell ref="E7:E11"/>
-    <mergeCell ref="F7:F11"/>
-    <mergeCell ref="G7:G11"/>
-    <mergeCell ref="H7:H11"/>
-    <mergeCell ref="I17:I21"/>
-    <mergeCell ref="J17:J21"/>
-    <mergeCell ref="C24:C28"/>
-    <mergeCell ref="D24:D28"/>
-    <mergeCell ref="E24:E28"/>
-    <mergeCell ref="F24:F28"/>
-    <mergeCell ref="G24:G28"/>
-    <mergeCell ref="H24:H28"/>
-    <mergeCell ref="I24:I28"/>
-    <mergeCell ref="J24:J28"/>
-    <mergeCell ref="C17:C21"/>
-    <mergeCell ref="D17:D21"/>
-    <mergeCell ref="E17:E21"/>
-    <mergeCell ref="F17:F21"/>
-    <mergeCell ref="G17:G21"/>
-    <mergeCell ref="H17:H21"/>
-    <mergeCell ref="I29:I33"/>
-    <mergeCell ref="J29:J33"/>
-    <mergeCell ref="C34:C38"/>
-    <mergeCell ref="D34:D38"/>
-    <mergeCell ref="E34:E38"/>
-    <mergeCell ref="F34:F38"/>
-    <mergeCell ref="G34:G38"/>
-    <mergeCell ref="H34:H38"/>
-    <mergeCell ref="I34:I38"/>
-    <mergeCell ref="J34:J38"/>
-    <mergeCell ref="C29:C33"/>
-    <mergeCell ref="D29:D33"/>
-    <mergeCell ref="E29:E33"/>
-    <mergeCell ref="F29:F33"/>
-    <mergeCell ref="G29:G33"/>
-    <mergeCell ref="H29:H33"/>
-    <mergeCell ref="I40:I44"/>
-    <mergeCell ref="J40:J44"/>
-    <mergeCell ref="C45:C49"/>
-    <mergeCell ref="D45:D49"/>
-    <mergeCell ref="E45:E49"/>
-    <mergeCell ref="F45:F49"/>
-    <mergeCell ref="G45:G49"/>
-    <mergeCell ref="H45:H49"/>
-    <mergeCell ref="I45:I49"/>
-    <mergeCell ref="J45:J49"/>
-    <mergeCell ref="C40:C44"/>
-    <mergeCell ref="D40:D44"/>
-    <mergeCell ref="E40:E44"/>
-    <mergeCell ref="F40:F44"/>
-    <mergeCell ref="G40:G44"/>
-    <mergeCell ref="H40:H44"/>
-    <mergeCell ref="I50:I54"/>
-    <mergeCell ref="J50:J54"/>
-    <mergeCell ref="C56:C60"/>
-    <mergeCell ref="D56:D60"/>
-    <mergeCell ref="E56:E60"/>
-    <mergeCell ref="F56:F60"/>
-    <mergeCell ref="G56:G60"/>
-    <mergeCell ref="H56:H60"/>
-    <mergeCell ref="I56:I60"/>
-    <mergeCell ref="J56:J60"/>
-    <mergeCell ref="C50:C54"/>
-    <mergeCell ref="D50:D54"/>
-    <mergeCell ref="E50:E54"/>
-    <mergeCell ref="F50:F54"/>
-    <mergeCell ref="G50:G54"/>
-    <mergeCell ref="H50:H54"/>
-    <mergeCell ref="I61:I65"/>
-    <mergeCell ref="J61:J65"/>
-    <mergeCell ref="C66:C70"/>
-    <mergeCell ref="D66:D70"/>
-    <mergeCell ref="E66:E70"/>
-    <mergeCell ref="F66:F70"/>
-    <mergeCell ref="G66:G70"/>
-    <mergeCell ref="H66:H70"/>
-    <mergeCell ref="I66:I70"/>
-    <mergeCell ref="J66:J70"/>
-    <mergeCell ref="C61:C65"/>
-    <mergeCell ref="D61:D65"/>
-    <mergeCell ref="E61:E65"/>
-    <mergeCell ref="F61:F65"/>
-    <mergeCell ref="G61:G65"/>
-    <mergeCell ref="H61:H65"/>
     <mergeCell ref="I84:I88"/>
     <mergeCell ref="J84:J88"/>
     <mergeCell ref="C84:C88"/>
@@ -3853,6 +3764,102 @@
     <mergeCell ref="F74:F78"/>
     <mergeCell ref="G74:G78"/>
     <mergeCell ref="H74:H78"/>
+    <mergeCell ref="I61:I65"/>
+    <mergeCell ref="J61:J65"/>
+    <mergeCell ref="C66:C70"/>
+    <mergeCell ref="D66:D70"/>
+    <mergeCell ref="E66:E70"/>
+    <mergeCell ref="F66:F70"/>
+    <mergeCell ref="G66:G70"/>
+    <mergeCell ref="H66:H70"/>
+    <mergeCell ref="I66:I70"/>
+    <mergeCell ref="J66:J70"/>
+    <mergeCell ref="C61:C65"/>
+    <mergeCell ref="D61:D65"/>
+    <mergeCell ref="E61:E65"/>
+    <mergeCell ref="F61:F65"/>
+    <mergeCell ref="G61:G65"/>
+    <mergeCell ref="H61:H65"/>
+    <mergeCell ref="I50:I54"/>
+    <mergeCell ref="J50:J54"/>
+    <mergeCell ref="C56:C60"/>
+    <mergeCell ref="D56:D60"/>
+    <mergeCell ref="E56:E60"/>
+    <mergeCell ref="F56:F60"/>
+    <mergeCell ref="G56:G60"/>
+    <mergeCell ref="H56:H60"/>
+    <mergeCell ref="I56:I60"/>
+    <mergeCell ref="J56:J60"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="D50:D54"/>
+    <mergeCell ref="E50:E54"/>
+    <mergeCell ref="F50:F54"/>
+    <mergeCell ref="G50:G54"/>
+    <mergeCell ref="H50:H54"/>
+    <mergeCell ref="I40:I44"/>
+    <mergeCell ref="J40:J44"/>
+    <mergeCell ref="C45:C49"/>
+    <mergeCell ref="D45:D49"/>
+    <mergeCell ref="E45:E49"/>
+    <mergeCell ref="F45:F49"/>
+    <mergeCell ref="G45:G49"/>
+    <mergeCell ref="H45:H49"/>
+    <mergeCell ref="I45:I49"/>
+    <mergeCell ref="J45:J49"/>
+    <mergeCell ref="C40:C44"/>
+    <mergeCell ref="D40:D44"/>
+    <mergeCell ref="E40:E44"/>
+    <mergeCell ref="F40:F44"/>
+    <mergeCell ref="G40:G44"/>
+    <mergeCell ref="H40:H44"/>
+    <mergeCell ref="I29:I33"/>
+    <mergeCell ref="J29:J33"/>
+    <mergeCell ref="C34:C38"/>
+    <mergeCell ref="D34:D38"/>
+    <mergeCell ref="E34:E38"/>
+    <mergeCell ref="F34:F38"/>
+    <mergeCell ref="G34:G38"/>
+    <mergeCell ref="H34:H38"/>
+    <mergeCell ref="I34:I38"/>
+    <mergeCell ref="J34:J38"/>
+    <mergeCell ref="C29:C33"/>
+    <mergeCell ref="D29:D33"/>
+    <mergeCell ref="E29:E33"/>
+    <mergeCell ref="F29:F33"/>
+    <mergeCell ref="G29:G33"/>
+    <mergeCell ref="H29:H33"/>
+    <mergeCell ref="I17:I21"/>
+    <mergeCell ref="J17:J21"/>
+    <mergeCell ref="C24:C28"/>
+    <mergeCell ref="D24:D28"/>
+    <mergeCell ref="E24:E28"/>
+    <mergeCell ref="F24:F28"/>
+    <mergeCell ref="G24:G28"/>
+    <mergeCell ref="H24:H28"/>
+    <mergeCell ref="I24:I28"/>
+    <mergeCell ref="J24:J28"/>
+    <mergeCell ref="C17:C21"/>
+    <mergeCell ref="D17:D21"/>
+    <mergeCell ref="E17:E21"/>
+    <mergeCell ref="F17:F21"/>
+    <mergeCell ref="G17:G21"/>
+    <mergeCell ref="H17:H21"/>
+    <mergeCell ref="I7:I11"/>
+    <mergeCell ref="J7:J11"/>
+    <mergeCell ref="C12:C16"/>
+    <mergeCell ref="D12:D16"/>
+    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="F12:F16"/>
+    <mergeCell ref="G12:G16"/>
+    <mergeCell ref="H12:H16"/>
+    <mergeCell ref="I12:I16"/>
+    <mergeCell ref="J12:J16"/>
+    <mergeCell ref="C7:C11"/>
+    <mergeCell ref="D7:D11"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="F7:F11"/>
+    <mergeCell ref="G7:G11"/>
+    <mergeCell ref="H7:H11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
